--- a/data/trans_dic/P38C-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P38C-Provincia-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de glucosal por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de glucosal por prescripción médica (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,24; 75,84</t>
+          <t>64,91; 75,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,52; 98,83</t>
+          <t>93,4; 98,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,36; 80,97</t>
+          <t>70,62; 80,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96,21; 99,34</t>
+          <t>95,99; 99,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>69,54; 76,96</t>
+          <t>69,3; 77,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,76; 98,82</t>
+          <t>95,63; 98,81</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,27; 90,52</t>
+          <t>84,38; 90,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,74; 79,75</t>
+          <t>67,76; 79,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91,81; 96,02</t>
+          <t>91,84; 96,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80,41; 87,15</t>
+          <t>80,81; 87,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,31; 92,82</t>
+          <t>89,38; 92,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,42; 82,65</t>
+          <t>75,64; 82,6</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86,06; 92,6</t>
+          <t>85,67; 92,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,71; 96,31</t>
+          <t>89,94; 96,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,2; 95,01</t>
+          <t>89,22; 94,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>95,36; 98,99</t>
+          <t>95,12; 98,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,45; 92,74</t>
+          <t>88,62; 92,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>93,64; 97,14</t>
+          <t>93,5; 97,31</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,76; 95,08</t>
+          <t>89,55; 94,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,91; 91,33</t>
+          <t>76,75; 90,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88,31; 94,22</t>
+          <t>88,6; 94,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47,42; 93,31</t>
+          <t>47,1; 93,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,86; 93,8</t>
+          <t>90,09; 94,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,62; 90,67</t>
+          <t>60,01; 90,79</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,04; 82,67</t>
+          <t>70,87; 82,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>74,69; 86,5</t>
+          <t>75,03; 86,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84,19; 92,42</t>
+          <t>84,07; 92,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83,89; 91,71</t>
+          <t>83,43; 91,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>79,35; 86,29</t>
+          <t>79,28; 86,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,52; 88,13</t>
+          <t>81,57; 88,25</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>75,52; 85,16</t>
+          <t>75,58; 85,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91,32; 97,64</t>
+          <t>91,04; 97,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83,12; 91,11</t>
+          <t>82,94; 91,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>94,48; 98,94</t>
+          <t>94,18; 98,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>80,86; 87,18</t>
+          <t>80,62; 86,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>93,94; 97,77</t>
+          <t>94,06; 97,79</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>59,96; 68,01</t>
+          <t>60,3; 68,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>76,0; 85,71</t>
+          <t>76,33; 85,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70,25; 76,85</t>
+          <t>69,98; 77,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90,13; 97,05</t>
+          <t>90,07; 97,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>66,14; 71,44</t>
+          <t>66,18; 71,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,95; 92,84</t>
+          <t>85,05; 92,64</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>87,03; 91,36</t>
+          <t>86,62; 91,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,05; 62,88</t>
+          <t>21,44; 63,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>92,37; 95,66</t>
+          <t>92,61; 95,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66,16; 72,63</t>
+          <t>66,46; 72,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>90,45; 93,22</t>
+          <t>90,32; 93,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,96; 66,41</t>
+          <t>34,78; 66,48</t>
         </is>
       </c>
     </row>
@@ -1277,27 +1277,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>57,23; 80,95</t>
+          <t>58,16; 81,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86,35; 88,57</t>
+          <t>86,35; 88,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80,73; 88,75</t>
+          <t>80,58; 88,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>83,65; 85,33</t>
+          <t>83,65; 85,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>70,67; 84,5</t>
+          <t>72,13; 84,41</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de glucosal por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de glucosal por prescripción médica (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1506,32 +1506,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>185615; 219118</t>
+          <t>187533; 218591</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>291269; 307797</t>
+          <t>290890; 307306</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>202523; 233056</t>
+          <t>203264; 232394</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>278645; 287713</t>
+          <t>278035; 287749</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>401071; 443845</t>
+          <t>399668; 445351</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>575582; 593966</t>
+          <t>574809; 593919</t>
         </is>
       </c>
     </row>
@@ -1624,32 +1624,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>416648; 447533</t>
+          <t>417168; 447557</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>350165; 412202</t>
+          <t>350247; 411487</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>478436; 500350</t>
+          <t>478596; 500785</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>413646; 448282</t>
+          <t>415710; 451084</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>906929; 942635</t>
+          <t>907663; 941453</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>777842; 852410</t>
+          <t>780092; 851887</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>274161; 294992</t>
+          <t>272912; 293808</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>283521; 304387</t>
+          <t>284270; 304917</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>299156; 318647</t>
+          <t>299237; 317782</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>332939; 345597</t>
+          <t>332107; 345382</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>578396; 606451</t>
+          <t>579539; 606978</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>622845; 646151</t>
+          <t>621948; 647313</t>
         </is>
       </c>
     </row>
@@ -1860,32 +1860,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>329373; 348914</t>
+          <t>328618; 347859</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>240377; 285451</t>
+          <t>239882; 283928</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>340936; 363771</t>
+          <t>342066; 362938</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>224045; 440894</t>
+          <t>222547; 440122</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>676659; 706374</t>
+          <t>678384; 707916</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>452360; 711793</t>
+          <t>471091; 712753</t>
         </is>
       </c>
     </row>
@@ -1978,32 +1978,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>150042; 174612</t>
+          <t>149682; 174607</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>133503; 154604</t>
+          <t>134107; 154376</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>184022; 202028</t>
+          <t>183765; 202129</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>174713; 191012</t>
+          <t>173763; 190664</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>341036; 370866</t>
+          <t>340750; 371790</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>315510; 341063</t>
+          <t>315703; 341540</t>
         </is>
       </c>
     </row>
@@ -2096,32 +2096,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>197228; 222393</t>
+          <t>197375; 221993</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>246221; 263278</t>
+          <t>245476; 263030</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>225549; 247238</t>
+          <t>225075; 247681</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>241825; 253256</t>
+          <t>241070; 253107</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>430616; 464253</t>
+          <t>429343; 463221</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>493768; 513898</t>
+          <t>494396; 513992</t>
         </is>
       </c>
     </row>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>388511; 440668</t>
+          <t>390688; 441428</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>474441; 535059</t>
+          <t>476521; 532089</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>480648; 525837</t>
+          <t>478796; 526950</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>762991; 821615</t>
+          <t>762519; 822653</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>881092; 951641</t>
+          <t>881659; 952784</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1249468; 1365518</t>
+          <t>1250990; 1362619</t>
         </is>
       </c>
     </row>
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>669147; 702483</t>
+          <t>666015; 700866</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>186164; 583943</t>
+          <t>199134; 586401</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>760371; 787478</t>
+          <t>762358; 789218</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>474865; 521270</t>
+          <t>477014; 522240</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1440080; 1484149</t>
+          <t>1438026; 1481433</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>575614; 1093435</t>
+          <t>572678; 1094493</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2689338; 2782281</t>
+          <t>2689455; 2781973</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1979099; 2799393</t>
+          <t>2011517; 2802762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3046246; 3124396</t>
+          <t>3046105; 3120388</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2949914; 3243177</t>
+          <t>2944456; 3237367</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5759974; 5875968</t>
+          <t>5760286; 5881794</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5026322; 6009920</t>
+          <t>5130186; 6003651</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P38C-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P38C-Provincia-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,91; 75,66</t>
+          <t>64,03; 75,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,4; 98,67</t>
+          <t>94,38; 98,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,62; 80,74</t>
+          <t>70,06; 80,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95,99; 99,35</t>
+          <t>97,04; 99,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>69,3; 77,22</t>
+          <t>69,23; 76,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,63; 98,81</t>
+          <t>96,73; 99,0</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,72%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,38; 90,52</t>
+          <t>84,48; 90,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,76; 79,61</t>
+          <t>69,24; 80,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91,84; 96,1</t>
+          <t>91,86; 95,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80,81; 87,69</t>
+          <t>80,05; 87,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,38; 92,71</t>
+          <t>89,05; 92,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,64; 82,6</t>
+          <t>76,13; 82,65</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>85,67; 92,23</t>
+          <t>85,36; 92,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,94; 96,48</t>
+          <t>89,95; 96,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,22; 94,75</t>
+          <t>89,19; 94,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>95,12; 98,93</t>
+          <t>94,92; 98,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,62; 92,82</t>
+          <t>88,68; 92,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>93,5; 97,31</t>
+          <t>93,56; 97,21</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>87,85%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,55; 94,8</t>
+          <t>89,41; 94,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,75; 90,84</t>
+          <t>76,1; 89,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88,6; 94,01</t>
+          <t>88,47; 94,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47,1; 93,15</t>
+          <t>87,67; 94,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,09; 94,01</t>
+          <t>90,04; 93,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,01; 90,79</t>
+          <t>83,94; 90,44</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>82,47%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>70,87; 82,67</t>
+          <t>70,93; 82,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>75,03; 86,37</t>
+          <t>71,99; 82,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84,07; 92,47</t>
+          <t>84,29; 92,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83,43; 91,54</t>
+          <t>81,89; 90,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>79,28; 86,5</t>
+          <t>78,82; 86,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,57; 88,25</t>
+          <t>78,74; 85,89</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>75,58; 85,0</t>
+          <t>75,46; 85,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91,04; 97,55</t>
+          <t>89,62; 96,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>82,94; 91,27</t>
+          <t>83,14; 91,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>94,18; 98,88</t>
+          <t>93,95; 98,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>80,62; 86,99</t>
+          <t>80,66; 87,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>94,06; 97,79</t>
+          <t>92,98; 96,95</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>86,9%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>60,3; 68,13</t>
+          <t>60,02; 67,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>76,33; 85,23</t>
+          <t>78,54; 85,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69,98; 77,02</t>
+          <t>70,13; 76,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90,07; 97,18</t>
+          <t>88,43; 92,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>66,18; 71,52</t>
+          <t>66,38; 71,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,05; 92,64</t>
+          <t>84,62; 89,0</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>64,49%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>86,62; 91,15</t>
+          <t>86,25; 91,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,44; 63,14</t>
+          <t>55,61; 63,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>92,61; 95,87</t>
+          <t>92,6; 95,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66,46; 72,76</t>
+          <t>65,7; 72,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>90,32; 93,05</t>
+          <t>90,44; 93,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,78; 66,48</t>
+          <t>62,13; 66,89</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>80,09; 82,85</t>
+          <t>79,87; 82,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>58,16; 81,04</t>
+          <t>77,73; 81,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86,35; 88,45</t>
+          <t>86,21; 88,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80,58; 88,59</t>
+          <t>85,37; 87,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>83,65; 85,42</t>
+          <t>83,63; 85,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>72,13; 84,41</t>
+          <t>81,94; 84,0</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>301984</t>
+          <t>310678</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284965</t>
+          <t>311718</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>586948</t>
+          <t>622396</t>
         </is>
       </c>
     </row>
@@ -1506,32 +1506,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>187533; 218591</t>
+          <t>184982; 219275</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>290890; 307306</t>
+          <t>300919; 315105</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>203264; 232394</t>
+          <t>201647; 232372</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>278035; 287749</t>
+          <t>306704; 314129</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>399668; 445351</t>
+          <t>399290; 442951</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>574809; 593919</t>
+          <t>614144; 628557</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>383983</t>
+          <t>397879</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>434193</t>
+          <t>459237</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>818176</t>
+          <t>857116</t>
         </is>
       </c>
     </row>
@@ -1624,32 +1624,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>417168; 447557</t>
+          <t>417671; 447307</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>350247; 411487</t>
+          <t>366451; 425764</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>478596; 500785</t>
+          <t>478691; 499879</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>415710; 451084</t>
+          <t>436985; 477106</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>907663; 941453</t>
+          <t>904290; 942349</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>780092; 851887</t>
+          <t>818540; 888614</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>296205</t>
+          <t>296241</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>340754</t>
+          <t>347043</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>636959</t>
+          <t>643285</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>272912; 293808</t>
+          <t>271942; 293715</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>284270; 304917</t>
+          <t>284240; 304897</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>299237; 317782</t>
+          <t>299133; 317896</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>332107; 345382</t>
+          <t>338262; 352185</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>579539; 606978</t>
+          <t>579900; 607796</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>621948; 647313</t>
+          <t>629057; 653617</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>268937</t>
+          <t>312927</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>371831</t>
+          <t>382436</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>640768</t>
+          <t>695364</t>
         </is>
       </c>
     </row>
@@ -1860,32 +1860,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>328618; 347859</t>
+          <t>328085; 348186</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>239882; 283928</t>
+          <t>283967; 332122</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>342066; 362938</t>
+          <t>341582; 363443</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>222547; 440122</t>
+          <t>366784; 393317</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>678384; 707916</t>
+          <t>678000; 707421</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>471091; 712753</t>
+          <t>664414; 715793</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>145723</t>
+          <t>160360</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>183687</t>
+          <t>196305</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>329410</t>
+          <t>356665</t>
         </is>
       </c>
     </row>
@@ -1978,32 +1978,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>149682; 174607</t>
+          <t>149813; 174796</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>134107; 154376</t>
+          <t>148050; 170650</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>183765; 202129</t>
+          <t>184256; 201688</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>173763; 190664</t>
+          <t>185737; 204997</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>340750; 371790</t>
+          <t>338775; 370686</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>315703; 341540</t>
+          <t>340542; 371459</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>257149</t>
+          <t>252982</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>249192</t>
+          <t>255091</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>506341</t>
+          <t>508073</t>
         </is>
       </c>
     </row>
@@ -2096,32 +2096,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>197375; 221993</t>
+          <t>197074; 222065</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>245476; 263030</t>
+          <t>242594; 260083</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>225075; 247681</t>
+          <t>225621; 247009</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>241070; 253107</t>
+          <t>246681; 259428</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>429343; 463221</t>
+          <t>429507; 464056</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>494396; 513992</t>
+          <t>495837; 517000</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>507850</t>
+          <t>594350</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>789078</t>
+          <t>697312</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1296929</t>
+          <t>1291662</t>
         </is>
       </c>
     </row>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>390688; 441428</t>
+          <t>388883; 440033</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>476521; 532089</t>
+          <t>565208; 617993</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>478796; 526950</t>
+          <t>479844; 524967</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>762519; 822653</t>
+          <t>677965; 711799</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>881659; 952784</t>
+          <t>884241; 952506</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1250990; 1362619</t>
+          <t>1257800; 1322885</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>420425</t>
+          <t>476972</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>499939</t>
+          <t>573808</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>920365</t>
+          <t>1050780</t>
         </is>
       </c>
     </row>
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>666015; 700866</t>
+          <t>663185; 700467</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>199134; 586401</t>
+          <t>443821; 507121</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>762358; 789218</t>
+          <t>762323; 788705</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>477014; 522240</t>
+          <t>546152; 599475</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1438026; 1481433</t>
+          <t>1439906; 1482786</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>572678; 1094493</t>
+          <t>1012344; 1089919</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2582257</t>
+          <t>2802391</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3153638</t>
+          <t>3222951</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5735894</t>
+          <t>6025342</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2689455; 2781973</t>
+          <t>2682118; 2780488</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2011517; 2802762</t>
+          <t>2744836; 2860933</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3046105; 3120388</t>
+          <t>3041339; 3123681</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2944456; 3237367</t>
+          <t>3179365; 3264943</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5760286; 5881794</t>
+          <t>5758371; 5881600</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5130186; 6003651</t>
+          <t>5945412; 6094685</t>
         </is>
       </c>
     </row>
